--- a/Result/profitability/5534.xlsx
+++ b/Result/profitability/5534.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>1.675</v>
+        <v>1.6375</v>
       </c>
       <c r="N2" t="n">
-        <v>36.855</v>
+        <v>37.62875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>3.87</v>
       </c>
       <c r="M3" t="n">
-        <v>2.01625</v>
+        <v>1.48</v>
       </c>
       <c r="N3" t="n">
-        <v>39.705</v>
+        <v>38.36125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.48</v>
       </c>
       <c r="M4" t="n">
-        <v>1.56</v>
+        <v>1.55625</v>
       </c>
       <c r="N4" t="n">
-        <v>40.90000000000001</v>
+        <v>37.975</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -914,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>2.02</v>
       </c>
       <c r="M5" t="n">
-        <v>1.70375</v>
+        <v>1.7975</v>
       </c>
       <c r="N5" t="n">
-        <v>39.3775</v>
+        <v>38.73125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.98</v>
       </c>
       <c r="M6" t="n">
-        <v>1.94</v>
+        <v>1.885</v>
       </c>
       <c r="N6" t="n">
-        <v>39.87625</v>
+        <v>38.40625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.23</v>
       </c>
       <c r="M7" t="n">
-        <v>1.80875</v>
+        <v>1.44375</v>
       </c>
       <c r="N7" t="n">
-        <v>39.4975</v>
+        <v>39.04625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.49</v>
       </c>
       <c r="M8" t="n">
-        <v>1.525</v>
+        <v>1.60625</v>
       </c>
       <c r="N8" t="n">
-        <v>39.485</v>
+        <v>40.14625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>1.98125</v>
       </c>
       <c r="N11" t="n">
-        <v>43.32125</v>
+        <v>43.32125000000001</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5534</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1444</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1005</v>
+      </c>
+      <c r="E75" t="n">
+        <v>440</v>
+      </c>
+      <c r="F75" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="G75" t="n">
+        <v>330</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>22.82%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>335</v>
+      </c>
+      <c r="K75" t="n">
+        <v>264</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.6625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>35.86125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.6499999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>3.421052631578947</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.289999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2101708382995628</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>8.333333333333334</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-5.170000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1451024417625597</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
